--- a/results/CKI_Tables_NC.xlsx
+++ b/results/CKI_Tables_NC.xlsx
@@ -429,7 +429,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 1. Cross-organ conservation ranking by cell type (Tabula Sapiens, n=59 same-cell-type cross-organ pairs). Well-sampled cell types (n ≥ 5 cross-organ pairs) are ranked first by mean ω; sparsely sampled cell types (n &lt; 5 pairs; SD shown only where n &gt; 1) are listed below the divider, and their rankings should be interpreted as suggestive only. Because the k_n anchor is not calibrated across cell types (Discussion), cross-type gaps in mean ω are descriptive rather than calibrated. k_f-only controls for this ranking are reported in Supplementary Note 9.</t>
+          <t>Table 1. Cross-organ conservation ranking by cell type (Tabula Sapiens, n=59 same-cell-type cross-organ pairs). Well-sampled cell types (n ≥ 5 cross-organ pairs) are ranked first by mean ω; sparsely sampled cell types (n &lt; 5 pairs; SD shown only where n &gt; 1) are listed below the divider, and their rankings should be interpreted as suggestive only. Because the k_n anchor is not calibrated across cell types (Discussion), cross-type gaps in mean ω are descriptive rather than calibrated. k_f-only controls for this ranking are reported in Supplementary Note 5.</t>
         </is>
       </c>
     </row>
